--- a/Loan_Portfolio_Dashboard.xlsx
+++ b/Loan_Portfolio_Dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data Science\Credit Analyst Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1033705-FF8A-4F43-B5A3-BF8A76F5D91D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEBB37E1-8906-4AA4-9858-17330243DBB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="745" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,8 +17,8 @@
     <sheet name="Loan Book" sheetId="2" r:id="rId2"/>
     <sheet name="Portfolio Summary" sheetId="4" r:id="rId3"/>
     <sheet name="Officer Performance" sheetId="5" r:id="rId4"/>
-    <sheet name="Charts &amp; Visuals" sheetId="6" r:id="rId5"/>
-    <sheet name="Executive Summary" sheetId="3" r:id="rId6"/>
+    <sheet name="Executive Summary" sheetId="3" r:id="rId5"/>
+    <sheet name="Charts &amp; Visuals" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Loan Book'!$A$1:$R$51</definedName>
@@ -1674,7 +1674,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="114">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1911,10 +1911,10 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1925,27 +1925,39 @@
     <xf numFmtId="0" fontId="11" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="27" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="31" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1966,24 +1978,6 @@
     </xf>
     <xf numFmtId="10" fontId="30" fillId="16" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2417,7 +2411,7 @@
               <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>Active</c:v>
+                  <c:v>Written Off</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>Closed</c:v>
@@ -2426,7 +2420,7 @@
                   <c:v>Delinquent</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Written Off</c:v>
+                  <c:v>Active</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2438,7 +2432,7 @@
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>22</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>10</c:v>
@@ -2447,7 +2441,7 @@
                   <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4</c:v>
+                  <c:v>22</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2642,25 +2636,25 @@
               <c:strCache>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
+                  <c:v>Education</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>Agriculture</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>Trade &amp; Commerce</c:v>
-                </c:pt>
                 <c:pt idx="2">
-                  <c:v>Manufacturing</c:v>
+                  <c:v>Transport</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Education</c:v>
+                  <c:v>Trade &amp; Commerce</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>Health</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>Real Estate</c:v>
+                  <c:v>Manufacturing</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>Transport</c:v>
+                  <c:v>Real Estate</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>Personal</c:v>
@@ -2675,25 +2669,25 @@
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
+                  <c:v>330000</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>353000</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>461000</c:v>
-                </c:pt>
                 <c:pt idx="2">
-                  <c:v>1200000</c:v>
+                  <c:v>435000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>330000</c:v>
+                  <c:v>461000</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>530000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1256000</c:v>
+                  <c:v>1200000</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>435000</c:v>
+                  <c:v>1256000</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>1353000</c:v>
@@ -3207,28 +3201,28 @@
               <c:strCache>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
+                  <c:v>S. Mutua</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>J. Kariuki</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
+                  <c:v>R. Njenga</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>M. Otieno</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>A. Wanjiku</c:v>
-                </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>P. Kimani</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>S. Mutua</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>L. Odhiambo</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>R. Njenga</c:v>
+                  <c:v>T. Chelimo</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>T. Chelimo</c:v>
+                  <c:v>A. Wanjiku</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3240,28 +3234,28 @@
                 <c:formatCode>0.0%</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
+                  <c:v>7.1698113207547168E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>0.27762039660056659</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
+                  <c:v>0.34482758620689657</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>0.37527114967462039</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.75249999999999995</c:v>
-                </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>0.39393939393939392</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>7.1698113207547168E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0.39649681528662423</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.34482758620689657</c:v>
+                  <c:v>0.47597930524759791</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.47597930524759791</c:v>
+                  <c:v>0.75249999999999995</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6712,34 +6706,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="94" t="s">
+      <c r="A1" s="89" t="s">
         <v>298</v>
       </c>
-      <c r="B1" s="94"/>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="94"/>
-      <c r="F1" s="94"/>
-      <c r="G1" s="94"/>
-      <c r="H1" s="94"/>
-      <c r="I1" s="94"/>
-      <c r="J1" s="94"/>
-      <c r="K1" s="94"/>
+      <c r="B1" s="89"/>
+      <c r="C1" s="89"/>
+      <c r="D1" s="89"/>
+      <c r="E1" s="89"/>
+      <c r="F1" s="89"/>
+      <c r="G1" s="89"/>
+      <c r="H1" s="89"/>
+      <c r="I1" s="89"/>
+      <c r="J1" s="89"/>
+      <c r="K1" s="89"/>
     </row>
     <row r="2" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="95" t="s">
+      <c r="A2" s="90" t="s">
         <v>299</v>
       </c>
-      <c r="B2" s="95"/>
-      <c r="C2" s="95"/>
-      <c r="D2" s="95"/>
-      <c r="E2" s="95"/>
-      <c r="F2" s="95"/>
-      <c r="G2" s="95"/>
-      <c r="H2" s="95"/>
-      <c r="I2" s="95"/>
-      <c r="J2" s="95"/>
-      <c r="K2" s="95"/>
+      <c r="B2" s="90"/>
+      <c r="C2" s="90"/>
+      <c r="D2" s="90"/>
+      <c r="E2" s="90"/>
+      <c r="F2" s="90"/>
+      <c r="G2" s="90"/>
+      <c r="H2" s="90"/>
+      <c r="I2" s="90"/>
+      <c r="J2" s="90"/>
+      <c r="K2" s="90"/>
     </row>
     <row r="4" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="92" t="s">
@@ -6748,12 +6742,12 @@
       <c r="C4" s="92"/>
       <c r="D4" s="92"/>
       <c r="E4" s="92"/>
-      <c r="G4" s="96" t="s">
+      <c r="G4" s="94" t="s">
         <v>301</v>
       </c>
-      <c r="H4" s="96"/>
-      <c r="I4" s="96"/>
-      <c r="J4" s="96"/>
+      <c r="H4" s="94"/>
+      <c r="I4" s="94"/>
+      <c r="J4" s="94"/>
     </row>
     <row r="5" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="20" t="s">
@@ -7006,12 +7000,12 @@
         <f>IFERROR(D13/SUM(D6:D13),0)</f>
         <v>0.22862453531598512</v>
       </c>
-      <c r="G13" s="97" t="s">
+      <c r="G13" s="95" t="s">
         <v>308</v>
       </c>
-      <c r="H13" s="97"/>
-      <c r="I13" s="97"/>
-      <c r="J13" s="97"/>
+      <c r="H13" s="95"/>
+      <c r="I13" s="95"/>
+      <c r="J13" s="95"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="B14" s="32" t="s">
@@ -7347,7 +7341,7 @@
     <mergeCell ref="G13:J13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7369,30 +7363,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="94" t="s">
+      <c r="A1" s="89" t="s">
         <v>339</v>
       </c>
-      <c r="B1" s="94"/>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="94"/>
-      <c r="F1" s="94"/>
-      <c r="G1" s="94"/>
-      <c r="H1" s="94"/>
-      <c r="I1" s="94"/>
+      <c r="B1" s="89"/>
+      <c r="C1" s="89"/>
+      <c r="D1" s="89"/>
+      <c r="E1" s="89"/>
+      <c r="F1" s="89"/>
+      <c r="G1" s="89"/>
+      <c r="H1" s="89"/>
+      <c r="I1" s="89"/>
     </row>
     <row r="2" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="95" t="s">
+      <c r="A2" s="90" t="s">
         <v>340</v>
       </c>
-      <c r="B2" s="95"/>
-      <c r="C2" s="95"/>
-      <c r="D2" s="95"/>
-      <c r="E2" s="95"/>
-      <c r="F2" s="95"/>
-      <c r="G2" s="95"/>
-      <c r="H2" s="95"/>
-      <c r="I2" s="95"/>
+      <c r="B2" s="90"/>
+      <c r="C2" s="90"/>
+      <c r="D2" s="90"/>
+      <c r="E2" s="90"/>
+      <c r="F2" s="90"/>
+      <c r="G2" s="90"/>
+      <c r="H2" s="90"/>
+      <c r="I2" s="90"/>
     </row>
     <row r="3" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="92" t="s">
@@ -7762,6 +7756,298 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FF117A65"/>
+  </sheetPr>
+  <dimension ref="A1:G32"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="6" width="22" customWidth="1"/>
+    <col min="7" max="7" width="3" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="89" t="s">
+        <v>273</v>
+      </c>
+      <c r="B1" s="89"/>
+      <c r="C1" s="89"/>
+      <c r="D1" s="89"/>
+      <c r="E1" s="89"/>
+      <c r="F1" s="89"/>
+      <c r="G1" s="89"/>
+    </row>
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="90" t="s">
+        <v>274</v>
+      </c>
+      <c r="B2" s="90"/>
+      <c r="C2" s="90"/>
+      <c r="D2" s="90"/>
+      <c r="E2" s="90"/>
+      <c r="F2" s="90"/>
+      <c r="G2" s="90"/>
+    </row>
+    <row r="3" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="4" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B4" s="94" t="s">
+        <v>275</v>
+      </c>
+      <c r="C4" s="94"/>
+      <c r="D4" s="94"/>
+      <c r="E4" s="94"/>
+      <c r="F4" s="94"/>
+      <c r="G4" s="94"/>
+    </row>
+    <row r="5" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="13" t="s">
+        <v>276</v>
+      </c>
+      <c r="C5" s="14">
+        <f>COUNTA('Loan Book'!A2:A51)</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B6" s="15" t="s">
+        <v>277</v>
+      </c>
+      <c r="C6" s="14">
+        <f>SUM('Loan Book'!F2:F51)</f>
+        <v>12750000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="13" t="s">
+        <v>278</v>
+      </c>
+      <c r="C7" s="14">
+        <f>SUM('Loan Book'!L2:L51)</f>
+        <v>5918000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="15" t="s">
+        <v>279</v>
+      </c>
+      <c r="C8" s="16">
+        <f>COUNTIF('Loan Book'!N2:N51,"Active")</f>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="13" t="s">
+        <v>280</v>
+      </c>
+      <c r="C9" s="17">
+        <f>COUNTIF('Loan Book'!N2:N51,"Delinquent")</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="15" t="s">
+        <v>281</v>
+      </c>
+      <c r="C10" s="17">
+        <f>COUNTIF('Loan Book'!N2:N51,"Written Off")</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="13" t="s">
+        <v>282</v>
+      </c>
+      <c r="C11" s="18">
+        <f>IFERROR(SUMPRODUCT(('Loan Book'!M2:M51&gt;30)*'Loan Book'!L2:L51)/SUM('Loan Book'!L2:L51),0)</f>
+        <v>0.44508279824264957</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="15" t="s">
+        <v>283</v>
+      </c>
+      <c r="C12" s="14">
+        <f>IFERROR(SUM('Loan Book'!F2:F51)/COUNTA('Loan Book'!A2:A51),0)</f>
+        <v>255000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="C13" s="19">
+        <f>AVERAGE('Loan Book'!J2:J51)</f>
+        <v>0.18817999999999993</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="C14" s="14">
+        <f>COUNTA('Officer Performance'!A4:A11)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="C15" s="14">
+        <f>COUNTA('Portfolio Summary'!A22:A29)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="15" t="s">
+        <v>287</v>
+      </c>
+      <c r="C16" s="14">
+        <f>COUNTA('Portfolio Summary'!A10:A17)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" ht="9" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="18" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B18" s="94" t="s">
+        <v>379</v>
+      </c>
+      <c r="C18" s="94"/>
+      <c r="D18" s="94"/>
+      <c r="E18" s="94"/>
+      <c r="F18" s="94"/>
+      <c r="G18" s="94"/>
+    </row>
+    <row r="19" spans="2:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="101" t="s">
+        <v>288</v>
+      </c>
+      <c r="C19" s="101"/>
+      <c r="D19" s="101"/>
+      <c r="E19" s="101"/>
+      <c r="F19" s="101"/>
+      <c r="G19" s="101"/>
+    </row>
+    <row r="20" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="97" t="s">
+        <v>289</v>
+      </c>
+      <c r="C20" s="97"/>
+      <c r="D20" s="97"/>
+      <c r="E20" s="97"/>
+      <c r="F20" s="97"/>
+      <c r="G20" s="97"/>
+    </row>
+    <row r="21" spans="2:7" ht="5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="22" spans="2:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="99" t="s">
+        <v>290</v>
+      </c>
+      <c r="C22" s="99"/>
+      <c r="D22" s="99"/>
+      <c r="E22" s="99"/>
+      <c r="F22" s="99"/>
+      <c r="G22" s="99"/>
+    </row>
+    <row r="23" spans="2:7" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B23" s="97" t="s">
+        <v>291</v>
+      </c>
+      <c r="C23" s="97"/>
+      <c r="D23" s="97"/>
+      <c r="E23" s="97"/>
+      <c r="F23" s="97"/>
+      <c r="G23" s="97"/>
+    </row>
+    <row r="24" spans="2:7" ht="6.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="25" spans="2:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B25" s="100" t="s">
+        <v>292</v>
+      </c>
+      <c r="C25" s="100"/>
+      <c r="D25" s="100"/>
+      <c r="E25" s="100"/>
+      <c r="F25" s="100"/>
+      <c r="G25" s="100"/>
+    </row>
+    <row r="26" spans="2:7" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B26" s="97" t="s">
+        <v>293</v>
+      </c>
+      <c r="C26" s="97"/>
+      <c r="D26" s="97"/>
+      <c r="E26" s="97"/>
+      <c r="F26" s="97"/>
+      <c r="G26" s="97"/>
+    </row>
+    <row r="27" spans="2:7" ht="3.5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="28" spans="2:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B28" s="96" t="s">
+        <v>294</v>
+      </c>
+      <c r="C28" s="96"/>
+      <c r="D28" s="96"/>
+      <c r="E28" s="96"/>
+      <c r="F28" s="96"/>
+      <c r="G28" s="96"/>
+    </row>
+    <row r="29" spans="2:7" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B29" s="97" t="s">
+        <v>295</v>
+      </c>
+      <c r="C29" s="97"/>
+      <c r="D29" s="97"/>
+      <c r="E29" s="97"/>
+      <c r="F29" s="97"/>
+      <c r="G29" s="97"/>
+    </row>
+    <row r="30" spans="2:7" ht="5" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="31" spans="2:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B31" s="98" t="s">
+        <v>296</v>
+      </c>
+      <c r="C31" s="98"/>
+      <c r="D31" s="98"/>
+      <c r="E31" s="98"/>
+      <c r="F31" s="98"/>
+      <c r="G31" s="98"/>
+    </row>
+    <row r="32" spans="2:7" ht="69" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B32" s="97" t="s">
+        <v>297</v>
+      </c>
+      <c r="C32" s="97"/>
+      <c r="D32" s="97"/>
+      <c r="E32" s="97"/>
+      <c r="F32" s="97"/>
+      <c r="G32" s="97"/>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B18:G18"/>
+    <mergeCell ref="B19:G19"/>
+    <mergeCell ref="B28:G28"/>
+    <mergeCell ref="B29:G29"/>
+    <mergeCell ref="B31:G31"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="B20:G20"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="B25:G25"/>
+    <mergeCell ref="B26:G26"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <tabColor rgb="FF6C3483"/>
@@ -7782,65 +8068,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="100" t="s">
+      <c r="A1" s="102" t="s">
         <v>370</v>
       </c>
-      <c r="B1" s="100"/>
-      <c r="C1" s="100"/>
-      <c r="D1" s="100"/>
-      <c r="E1" s="100"/>
-      <c r="F1" s="100"/>
-      <c r="G1" s="100"/>
-      <c r="H1" s="100"/>
-      <c r="I1" s="100"/>
-      <c r="J1" s="100"/>
-      <c r="K1" s="100"/>
-      <c r="L1" s="100"/>
-      <c r="M1" s="100"/>
-      <c r="N1" s="100"/>
-      <c r="O1" s="100"/>
-      <c r="P1" s="100"/>
-      <c r="Q1" s="100"/>
-      <c r="R1" s="100"/>
-      <c r="S1" s="100"/>
-      <c r="T1" s="100"/>
-      <c r="U1" s="100"/>
-      <c r="V1" s="100"/>
-      <c r="W1" s="100"/>
-      <c r="X1" s="100"/>
-      <c r="Y1" s="100"/>
-      <c r="Z1" s="100"/>
-      <c r="AA1" s="100"/>
+      <c r="B1" s="102"/>
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
+      <c r="L1" s="102"/>
+      <c r="M1" s="102"/>
+      <c r="N1" s="102"/>
+      <c r="O1" s="102"/>
+      <c r="P1" s="102"/>
+      <c r="Q1" s="102"/>
+      <c r="R1" s="102"/>
+      <c r="S1" s="102"/>
+      <c r="T1" s="102"/>
+      <c r="U1" s="102"/>
+      <c r="V1" s="102"/>
+      <c r="W1" s="102"/>
+      <c r="X1" s="102"/>
+      <c r="Y1" s="102"/>
+      <c r="Z1" s="102"/>
+      <c r="AA1" s="102"/>
     </row>
     <row r="2" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="103" t="s">
+      <c r="A2" s="107" t="s">
         <v>378</v>
       </c>
-      <c r="B2" s="103"/>
-      <c r="C2" s="103"/>
-      <c r="D2" s="103"/>
-      <c r="E2" s="103"/>
-      <c r="F2" s="103"/>
-      <c r="G2" s="103"/>
-      <c r="H2" s="103"/>
-      <c r="I2" s="103"/>
-      <c r="J2" s="103"/>
-      <c r="K2" s="103"/>
-      <c r="L2" s="103"/>
-      <c r="M2" s="103"/>
-      <c r="N2" s="103"/>
-      <c r="O2" s="103"/>
-      <c r="P2" s="103"/>
-      <c r="Q2" s="103"/>
-      <c r="R2" s="103"/>
-      <c r="S2" s="103"/>
-      <c r="T2" s="103"/>
-      <c r="U2" s="103"/>
-      <c r="V2" s="103"/>
-      <c r="W2" s="103"/>
-      <c r="X2" s="103"/>
-      <c r="Y2" s="103"/>
-      <c r="Z2" s="103"/>
+      <c r="B2" s="107"/>
+      <c r="C2" s="107"/>
+      <c r="D2" s="107"/>
+      <c r="E2" s="107"/>
+      <c r="F2" s="107"/>
+      <c r="G2" s="107"/>
+      <c r="H2" s="107"/>
+      <c r="I2" s="107"/>
+      <c r="J2" s="107"/>
+      <c r="K2" s="107"/>
+      <c r="L2" s="107"/>
+      <c r="M2" s="107"/>
+      <c r="N2" s="107"/>
+      <c r="O2" s="107"/>
+      <c r="P2" s="107"/>
+      <c r="Q2" s="107"/>
+      <c r="R2" s="107"/>
+      <c r="S2" s="107"/>
+      <c r="T2" s="107"/>
+      <c r="U2" s="107"/>
+      <c r="V2" s="107"/>
+      <c r="W2" s="107"/>
+      <c r="X2" s="107"/>
+      <c r="Y2" s="107"/>
+      <c r="Z2" s="107"/>
       <c r="AA2" s="80"/>
     </row>
     <row r="3" spans="1:28" ht="6.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -7881,105 +8167,105 @@
       <c r="D4" s="71" t="s">
         <v>374</v>
       </c>
-      <c r="F4" s="98" t="s">
+      <c r="F4" s="103" t="s">
         <v>373</v>
       </c>
-      <c r="G4" s="98"/>
-      <c r="H4" s="98"/>
-      <c r="I4" s="98"/>
-      <c r="J4" s="98"/>
+      <c r="G4" s="103"/>
+      <c r="H4" s="103"/>
+      <c r="I4" s="103"/>
+      <c r="J4" s="103"/>
       <c r="K4" s="74"/>
-      <c r="L4" s="98" t="s">
+      <c r="L4" s="103" t="s">
         <v>372</v>
       </c>
-      <c r="M4" s="98"/>
-      <c r="N4" s="98"/>
-      <c r="O4" s="98"/>
-      <c r="P4" s="98"/>
-      <c r="Q4" s="98"/>
+      <c r="M4" s="103"/>
+      <c r="N4" s="103"/>
+      <c r="O4" s="103"/>
+      <c r="P4" s="103"/>
+      <c r="Q4" s="103"/>
       <c r="R4" s="70"/>
       <c r="S4" s="76"/>
-      <c r="T4" s="98" t="s">
+      <c r="T4" s="103" t="s">
         <v>371</v>
       </c>
-      <c r="U4" s="98"/>
-      <c r="V4" s="98"/>
+      <c r="U4" s="103"/>
+      <c r="V4" s="103"/>
       <c r="W4" s="72"/>
       <c r="X4" s="76"/>
-      <c r="Y4" s="98" t="s">
+      <c r="Y4" s="103" t="s">
         <v>377</v>
       </c>
-      <c r="Z4" s="98"/>
-      <c r="AA4" s="98"/>
+      <c r="Z4" s="103"/>
+      <c r="AA4" s="103"/>
     </row>
     <row r="5" spans="1:28" s="69" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="70"/>
-      <c r="B5" s="104">
+      <c r="B5" s="108">
         <f>'Executive Summary'!C5</f>
         <v>50</v>
       </c>
       <c r="C5" s="73"/>
-      <c r="D5" s="106">
+      <c r="D5" s="110">
         <f>'Executive Summary'!C6</f>
         <v>12750000</v>
       </c>
-      <c r="F5" s="107">
+      <c r="F5" s="111">
         <f>'Executive Summary'!C13</f>
         <v>0.18817999999999993</v>
       </c>
-      <c r="G5" s="107"/>
-      <c r="H5" s="107"/>
-      <c r="I5" s="107"/>
-      <c r="J5" s="107"/>
+      <c r="G5" s="111"/>
+      <c r="H5" s="111"/>
+      <c r="I5" s="111"/>
+      <c r="J5" s="111"/>
       <c r="K5" s="74"/>
-      <c r="L5" s="99" t="str">
+      <c r="L5" s="104" t="str">
         <f>INDEX('Officer Performance'!B5:B12,MATCH(MAX('Officer Performance'!D5:D12),'Officer Performance'!D5:D12,0))</f>
         <v>A. Wanjiku</v>
       </c>
-      <c r="M5" s="99"/>
-      <c r="N5" s="99"/>
-      <c r="O5" s="99"/>
-      <c r="P5" s="99"/>
-      <c r="Q5" s="99"/>
-      <c r="R5" s="99"/>
+      <c r="M5" s="104"/>
+      <c r="N5" s="104"/>
+      <c r="O5" s="104"/>
+      <c r="P5" s="104"/>
+      <c r="Q5" s="104"/>
+      <c r="R5" s="104"/>
       <c r="S5" s="76"/>
-      <c r="T5" s="99" t="str">
+      <c r="T5" s="104" t="str">
         <f>INDEX('Officer Performance'!B5:B12,MATCH(MIN('Officer Performance'!D5:D12),'Officer Performance'!D5:D12,0))</f>
         <v>P. Kimani</v>
       </c>
-      <c r="U5" s="99"/>
-      <c r="V5" s="99"/>
+      <c r="U5" s="104"/>
+      <c r="V5" s="104"/>
       <c r="W5" s="82"/>
       <c r="X5" s="76"/>
-      <c r="Y5" s="99" t="str">
+      <c r="Y5" s="104" t="str">
         <f>INDEX(B36:B43,MATCH(MAX(D36:D43),D36:D43,0))</f>
         <v>A. Wanjiku</v>
       </c>
-      <c r="Z5" s="99"/>
-      <c r="AA5" s="99"/>
+      <c r="Z5" s="104"/>
+      <c r="AA5" s="104"/>
     </row>
     <row r="6" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="105"/>
-      <c r="D6" s="106"/>
-      <c r="F6" s="107"/>
-      <c r="G6" s="107"/>
-      <c r="H6" s="107"/>
-      <c r="I6" s="107"/>
-      <c r="J6" s="107"/>
-      <c r="L6" s="99"/>
-      <c r="M6" s="99"/>
-      <c r="N6" s="99"/>
-      <c r="O6" s="99"/>
-      <c r="P6" s="99"/>
-      <c r="Q6" s="99"/>
-      <c r="R6" s="99"/>
-      <c r="T6" s="99"/>
-      <c r="U6" s="99"/>
-      <c r="V6" s="99"/>
+      <c r="B6" s="109"/>
+      <c r="D6" s="110"/>
+      <c r="F6" s="111"/>
+      <c r="G6" s="111"/>
+      <c r="H6" s="111"/>
+      <c r="I6" s="111"/>
+      <c r="J6" s="111"/>
+      <c r="L6" s="104"/>
+      <c r="M6" s="104"/>
+      <c r="N6" s="104"/>
+      <c r="O6" s="104"/>
+      <c r="P6" s="104"/>
+      <c r="Q6" s="104"/>
+      <c r="R6" s="104"/>
+      <c r="T6" s="104"/>
+      <c r="U6" s="104"/>
+      <c r="V6" s="104"/>
       <c r="W6" s="82"/>
-      <c r="Y6" s="99"/>
-      <c r="Z6" s="99"/>
-      <c r="AA6" s="99"/>
+      <c r="Y6" s="104"/>
+      <c r="Z6" s="104"/>
+      <c r="AA6" s="104"/>
     </row>
     <row r="7" spans="1:28" s="81" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="80"/>
@@ -8012,11 +8298,11 @@
       <c r="AB7" s="69"/>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="B8" s="101" t="s">
+      <c r="B8" s="105" t="s">
         <v>366</v>
       </c>
-      <c r="C8" s="102"/>
-      <c r="D8" s="102"/>
+      <c r="C8" s="106"/>
+      <c r="D8" s="106"/>
       <c r="E8" s="68"/>
       <c r="F8" s="68"/>
       <c r="G8" s="68"/>
@@ -8075,12 +8361,12 @@
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.35">
       <c r="B10" s="65" t="s">
-        <v>57</v>
+        <v>140</v>
       </c>
       <c r="C10" s="65"/>
       <c r="D10" s="66">
-        <f>COUNTIF('Loan Book'!N2:N51,"Active")</f>
-        <v>22</v>
+        <f>COUNTIF('Loan Book'!N2:N51,"Written Off")</f>
+        <v>4</v>
       </c>
       <c r="E10" s="68"/>
       <c r="F10" s="68"/>
@@ -8174,12 +8460,12 @@
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.35">
       <c r="B13" s="65" t="s">
-        <v>140</v>
+        <v>57</v>
       </c>
       <c r="C13" s="65"/>
       <c r="D13" s="66">
-        <f>COUNTIF('Loan Book'!N2:N51,"Written Off")</f>
-        <v>4</v>
+        <f>COUNTIF('Loan Book'!N2:N51,"Active")</f>
+        <v>22</v>
       </c>
       <c r="E13" s="68"/>
       <c r="F13" s="68"/>
@@ -8231,11 +8517,11 @@
       <c r="AA14" s="68"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="B15" s="101" t="s">
+      <c r="B15" s="105" t="s">
         <v>367</v>
       </c>
-      <c r="C15" s="102"/>
-      <c r="D15" s="102"/>
+      <c r="C15" s="106"/>
+      <c r="D15" s="106"/>
       <c r="E15" s="68"/>
       <c r="F15" s="68"/>
       <c r="G15" s="68"/>
@@ -8294,12 +8580,12 @@
     </row>
     <row r="17" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B17" s="65" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="C17" s="65"/>
       <c r="D17" s="66">
-        <f>SUMIF('Loan Book'!D2:D51,"Agriculture",'Loan Book'!L2:L51)</f>
-        <v>353000</v>
+        <f>SUMIF('Loan Book'!D2:D51,"Education",'Loan Book'!L2:L51)</f>
+        <v>330000</v>
       </c>
       <c r="E17" s="68"/>
       <c r="F17" s="68"/>
@@ -8327,12 +8613,12 @@
     </row>
     <row r="18" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B18" s="65" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C18" s="65"/>
       <c r="D18" s="66">
-        <f>SUMIF('Loan Book'!D2:D51,"Trade &amp; Commerce",'Loan Book'!L2:L51)</f>
-        <v>461000</v>
+        <f>SUMIF('Loan Book'!D2:D51,"Agriculture",'Loan Book'!L2:L51)</f>
+        <v>353000</v>
       </c>
       <c r="E18" s="68"/>
       <c r="F18" s="68"/>
@@ -8360,12 +8646,12 @@
     </row>
     <row r="19" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B19" s="65" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="C19" s="65"/>
       <c r="D19" s="66">
-        <f>SUMIF('Loan Book'!D2:D51,"Manufacturing",'Loan Book'!L2:L51)</f>
-        <v>1200000</v>
+        <f>SUMIF('Loan Book'!D2:D51,"Transport",'Loan Book'!L2:L51)</f>
+        <v>435000</v>
       </c>
       <c r="E19" s="68"/>
       <c r="F19" s="68"/>
@@ -8393,12 +8679,12 @@
     </row>
     <row r="20" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B20" s="65" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="C20" s="65"/>
       <c r="D20" s="66">
-        <f>SUMIF('Loan Book'!D2:D51,"Education",'Loan Book'!L2:L51)</f>
-        <v>330000</v>
+        <f>SUMIF('Loan Book'!D2:D51,"Trade &amp; Commerce",'Loan Book'!L2:L51)</f>
+        <v>461000</v>
       </c>
       <c r="E20" s="68"/>
       <c r="F20" s="68"/>
@@ -8459,12 +8745,12 @@
     </row>
     <row r="22" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B22" s="65" t="s">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="C22" s="65"/>
       <c r="D22" s="66">
-        <f>SUMIF('Loan Book'!D2:D51,"Real Estate",'Loan Book'!L2:L51)</f>
-        <v>1256000</v>
+        <f>SUMIF('Loan Book'!D2:D51,"Manufacturing",'Loan Book'!L2:L51)</f>
+        <v>1200000</v>
       </c>
       <c r="E22" s="68"/>
       <c r="F22" s="68"/>
@@ -8492,12 +8778,12 @@
     </row>
     <row r="23" spans="2:27" x14ac:dyDescent="0.35">
       <c r="B23" s="65" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="C23" s="65"/>
       <c r="D23" s="66">
-        <f>SUMIF('Loan Book'!D2:D51,"Transport",'Loan Book'!L2:L51)</f>
-        <v>435000</v>
+        <f>SUMIF('Loan Book'!D2:D51,"Real Estate",'Loan Book'!L2:L51)</f>
+        <v>1256000</v>
       </c>
       <c r="E23" s="68"/>
       <c r="F23" s="68"/>
@@ -8582,11 +8868,11 @@
       <c r="AA25" s="68"/>
     </row>
     <row r="26" spans="2:27" x14ac:dyDescent="0.35">
-      <c r="B26" s="101" t="s">
+      <c r="B26" s="105" t="s">
         <v>368</v>
       </c>
-      <c r="C26" s="102"/>
-      <c r="D26" s="102"/>
+      <c r="C26" s="106"/>
+      <c r="D26" s="106"/>
       <c r="E26" s="68"/>
       <c r="F26" s="68"/>
       <c r="G26" s="68"/>
@@ -8834,11 +9120,11 @@
       <c r="AA33" s="68"/>
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="B34" s="101" t="s">
+      <c r="B34" s="105" t="s">
         <v>369</v>
       </c>
-      <c r="C34" s="102"/>
-      <c r="D34" s="102"/>
+      <c r="C34" s="106"/>
+      <c r="D34" s="106"/>
       <c r="E34" s="68"/>
       <c r="F34" s="68"/>
       <c r="G34" s="68"/>
@@ -8897,12 +9183,12 @@
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.35">
       <c r="B36" s="65" t="s">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="C36" s="65"/>
-      <c r="D36" s="67" cm="1">
-        <f t="array" ref="D36">IFERROR(SUMPRODUCT(('Loan Book'!P2:P51="J. Kariuki")*('Loan Book'!M2:M51&gt;30)*'Loan Book'!L2:L51)/SUMIF('Loan Book'!P2:P51,"J. Kariuki",'Loan Book'!L2:L51),0)</f>
-        <v>0.27762039660056659</v>
+      <c r="D36" s="67">
+        <f>IFERROR(SUMPRODUCT(('Loan Book'!P2:P51="S. Mutua")*('Loan Book'!M2:M51&gt;30)*'Loan Book'!L2:L51)/SUMIF('Loan Book'!P2:P51,"S. Mutua",'Loan Book'!L2:L51),0)</f>
+        <v>7.1698113207547168E-2</v>
       </c>
       <c r="E36" s="68"/>
       <c r="F36" s="68"/>
@@ -8930,12 +9216,12 @@
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.35">
       <c r="B37" s="65" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C37" s="65"/>
-      <c r="D37" s="67">
-        <f>IFERROR(SUMPRODUCT(('Loan Book'!P2:P51="M. Otieno")*('Loan Book'!M2:M51&gt;30)*'Loan Book'!L2:L51)/SUMIF('Loan Book'!P2:P51,"M. Otieno",'Loan Book'!L2:L51),0)</f>
-        <v>0.37527114967462039</v>
+      <c r="D37" s="67" cm="1">
+        <f t="array" ref="D37">IFERROR(SUMPRODUCT(('Loan Book'!P2:P51="J. Kariuki")*('Loan Book'!M2:M51&gt;30)*'Loan Book'!L2:L51)/SUMIF('Loan Book'!P2:P51,"J. Kariuki",'Loan Book'!L2:L51),0)</f>
+        <v>0.27762039660056659</v>
       </c>
       <c r="E37" s="68"/>
       <c r="F37" s="68"/>
@@ -8963,12 +9249,12 @@
     </row>
     <row r="38" spans="1:27" x14ac:dyDescent="0.35">
       <c r="B38" s="65" t="s">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="C38" s="65"/>
       <c r="D38" s="67">
-        <f>IFERROR(SUMPRODUCT(('Loan Book'!P2:P51="A. Wanjiku")*('Loan Book'!M2:M51&gt;30)*'Loan Book'!L2:L51)/SUMIF('Loan Book'!P2:P51,"A. Wanjiku",'Loan Book'!L2:L51),0)</f>
-        <v>0.75249999999999995</v>
+        <f>IFERROR(SUMPRODUCT(('Loan Book'!P2:P51="R. Njenga")*('Loan Book'!M2:M51&gt;30)*'Loan Book'!L2:L51)/SUMIF('Loan Book'!P2:P51,"R. Njenga",'Loan Book'!L2:L51),0)</f>
+        <v>0.34482758620689657</v>
       </c>
       <c r="E38" s="68"/>
       <c r="F38" s="68"/>
@@ -8996,12 +9282,12 @@
     </row>
     <row r="39" spans="1:27" x14ac:dyDescent="0.35">
       <c r="B39" s="65" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="C39" s="65"/>
       <c r="D39" s="67">
-        <f>IFERROR(SUMPRODUCT(('Loan Book'!P2:P51="P. Kimani")*('Loan Book'!M2:M51&gt;30)*'Loan Book'!L2:L51)/SUMIF('Loan Book'!P2:P51,"P. Kimani",'Loan Book'!L2:L51),0)</f>
-        <v>0.39393939393939392</v>
+        <f>IFERROR(SUMPRODUCT(('Loan Book'!P2:P51="M. Otieno")*('Loan Book'!M2:M51&gt;30)*'Loan Book'!L2:L51)/SUMIF('Loan Book'!P2:P51,"M. Otieno",'Loan Book'!L2:L51),0)</f>
+        <v>0.37527114967462039</v>
       </c>
       <c r="E39" s="68"/>
       <c r="F39" s="68"/>
@@ -9029,12 +9315,12 @@
     </row>
     <row r="40" spans="1:27" x14ac:dyDescent="0.35">
       <c r="B40" s="65" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="C40" s="65"/>
       <c r="D40" s="67">
-        <f>IFERROR(SUMPRODUCT(('Loan Book'!P2:P51="S. Mutua")*('Loan Book'!M2:M51&gt;30)*'Loan Book'!L2:L51)/SUMIF('Loan Book'!P2:P51,"S. Mutua",'Loan Book'!L2:L51),0)</f>
-        <v>7.1698113207547168E-2</v>
+        <f>IFERROR(SUMPRODUCT(('Loan Book'!P2:P51="P. Kimani")*('Loan Book'!M2:M51&gt;30)*'Loan Book'!L2:L51)/SUMIF('Loan Book'!P2:P51,"P. Kimani",'Loan Book'!L2:L51),0)</f>
+        <v>0.39393939393939392</v>
       </c>
       <c r="E40" s="68"/>
       <c r="F40" s="68"/>
@@ -9095,12 +9381,12 @@
     </row>
     <row r="42" spans="1:27" x14ac:dyDescent="0.35">
       <c r="B42" s="65" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="C42" s="65"/>
       <c r="D42" s="67">
-        <f>IFERROR(SUMPRODUCT(('Loan Book'!P2:P51="R. Njenga")*('Loan Book'!M2:M51&gt;30)*'Loan Book'!L2:L51)/SUMIF('Loan Book'!P2:P51,"R. Njenga",'Loan Book'!L2:L51),0)</f>
-        <v>0.34482758620689657</v>
+        <f>IFERROR(SUMPRODUCT(('Loan Book'!P2:P51="T. Chelimo")*('Loan Book'!M2:M51&gt;30)*'Loan Book'!L2:L51)/SUMIF('Loan Book'!P2:P51,"T. Chelimo",'Loan Book'!L2:L51),0)</f>
+        <v>0.47597930524759791</v>
       </c>
       <c r="E42" s="68"/>
       <c r="F42" s="68"/>
@@ -9128,12 +9414,12 @@
     </row>
     <row r="43" spans="1:27" x14ac:dyDescent="0.35">
       <c r="B43" s="65" t="s">
-        <v>102</v>
+        <v>58</v>
       </c>
       <c r="C43" s="65"/>
       <c r="D43" s="67">
-        <f>IFERROR(SUMPRODUCT(('Loan Book'!P2:P51="T. Chelimo")*('Loan Book'!M2:M51&gt;30)*'Loan Book'!L2:L51)/SUMIF('Loan Book'!P2:P51,"T. Chelimo",'Loan Book'!L2:L51),0)</f>
-        <v>0.47597930524759791</v>
+        <f>IFERROR(SUMPRODUCT(('Loan Book'!P2:P51="A. Wanjiku")*('Loan Book'!M2:M51&gt;30)*'Loan Book'!L2:L51)/SUMIF('Loan Book'!P2:P51,"A. Wanjiku",'Loan Book'!L2:L51),0)</f>
+        <v>0.75249999999999995</v>
       </c>
       <c r="E43" s="68"/>
       <c r="F43" s="68"/>
@@ -9173,9 +9459,10 @@
       <c r="K45" s="79"/>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B36:D43">
+    <sortCondition ref="D36:D43"/>
+  </sortState>
   <mergeCells count="16">
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B26:D26"/>
     <mergeCell ref="B34:D34"/>
     <mergeCell ref="A2:Z2"/>
     <mergeCell ref="B8:D8"/>
@@ -9190,301 +9477,11 @@
     <mergeCell ref="A1:AA1"/>
     <mergeCell ref="Y4:AA4"/>
     <mergeCell ref="Y5:AA6"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B26:D26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <sheetPr>
-    <tabColor rgb="FF117A65"/>
-  </sheetPr>
-  <dimension ref="A1:G32"/>
-  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="3" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="94" t="s">
-        <v>273</v>
-      </c>
-      <c r="B1" s="94"/>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="94"/>
-      <c r="F1" s="94"/>
-      <c r="G1" s="94"/>
-    </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="95" t="s">
-        <v>274</v>
-      </c>
-      <c r="B2" s="95"/>
-      <c r="C2" s="95"/>
-      <c r="D2" s="95"/>
-      <c r="E2" s="95"/>
-      <c r="F2" s="95"/>
-      <c r="G2" s="95"/>
-    </row>
-    <row r="3" spans="1:7" ht="6" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="4" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="96" t="s">
-        <v>275</v>
-      </c>
-      <c r="C4" s="96"/>
-      <c r="D4" s="96"/>
-      <c r="E4" s="96"/>
-      <c r="F4" s="96"/>
-      <c r="G4" s="96"/>
-    </row>
-    <row r="5" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="13" t="s">
-        <v>276</v>
-      </c>
-      <c r="C5" s="14">
-        <f>COUNTA('Loan Book'!A2:A51)</f>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="15" t="s">
-        <v>277</v>
-      </c>
-      <c r="C6" s="14">
-        <f>SUM('Loan Book'!F2:F51)</f>
-        <v>12750000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="12.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="13" t="s">
-        <v>278</v>
-      </c>
-      <c r="C7" s="14">
-        <f>SUM('Loan Book'!L2:L51)</f>
-        <v>5918000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="15" t="s">
-        <v>279</v>
-      </c>
-      <c r="C8" s="16">
-        <f>COUNTIF('Loan Book'!N2:N51,"Active")</f>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="13" t="s">
-        <v>280</v>
-      </c>
-      <c r="C9" s="17">
-        <f>COUNTIF('Loan Book'!N2:N51,"Delinquent")</f>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="15" t="s">
-        <v>281</v>
-      </c>
-      <c r="C10" s="17">
-        <f>COUNTIF('Loan Book'!N2:N51,"Written Off")</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="13" t="s">
-        <v>282</v>
-      </c>
-      <c r="C11" s="18">
-        <f>IFERROR(SUMPRODUCT(('Loan Book'!M2:M51&gt;30)*'Loan Book'!L2:L51)/SUM('Loan Book'!L2:L51),0)</f>
-        <v>0.44508279824264957</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="15" t="s">
-        <v>283</v>
-      </c>
-      <c r="C12" s="14">
-        <f>IFERROR(SUM('Loan Book'!F2:F51)/COUNTA('Loan Book'!A2:A51),0)</f>
-        <v>255000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="13" t="s">
-        <v>284</v>
-      </c>
-      <c r="C13" s="19">
-        <f>AVERAGE('Loan Book'!J2:J51)</f>
-        <v>0.18817999999999993</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="15" t="s">
-        <v>285</v>
-      </c>
-      <c r="C14" s="14">
-        <f>COUNTA('Officer Performance'!A4:A11)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="13" t="s">
-        <v>286</v>
-      </c>
-      <c r="C15" s="14">
-        <f>COUNTA('Portfolio Summary'!A22:A29)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="15" t="s">
-        <v>287</v>
-      </c>
-      <c r="C16" s="14">
-        <f>COUNTA('Portfolio Summary'!A10:A17)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" ht="9" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="18" spans="2:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="96" t="s">
-        <v>379</v>
-      </c>
-      <c r="C18" s="96"/>
-      <c r="D18" s="96"/>
-      <c r="E18" s="96"/>
-      <c r="F18" s="96"/>
-      <c r="G18" s="96"/>
-    </row>
-    <row r="19" spans="2:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="113" t="s">
-        <v>288</v>
-      </c>
-      <c r="C19" s="113"/>
-      <c r="D19" s="113"/>
-      <c r="E19" s="113"/>
-      <c r="F19" s="113"/>
-      <c r="G19" s="113"/>
-    </row>
-    <row r="20" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="109" t="s">
-        <v>289</v>
-      </c>
-      <c r="C20" s="109"/>
-      <c r="D20" s="109"/>
-      <c r="E20" s="109"/>
-      <c r="F20" s="109"/>
-      <c r="G20" s="109"/>
-    </row>
-    <row r="21" spans="2:7" ht="5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="22" spans="2:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="111" t="s">
-        <v>290</v>
-      </c>
-      <c r="C22" s="111"/>
-      <c r="D22" s="111"/>
-      <c r="E22" s="111"/>
-      <c r="F22" s="111"/>
-      <c r="G22" s="111"/>
-    </row>
-    <row r="23" spans="2:7" ht="32.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="109" t="s">
-        <v>291</v>
-      </c>
-      <c r="C23" s="109"/>
-      <c r="D23" s="109"/>
-      <c r="E23" s="109"/>
-      <c r="F23" s="109"/>
-      <c r="G23" s="109"/>
-    </row>
-    <row r="24" spans="2:7" ht="6.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="25" spans="2:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="112" t="s">
-        <v>292</v>
-      </c>
-      <c r="C25" s="112"/>
-      <c r="D25" s="112"/>
-      <c r="E25" s="112"/>
-      <c r="F25" s="112"/>
-      <c r="G25" s="112"/>
-    </row>
-    <row r="26" spans="2:7" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="109" t="s">
-        <v>293</v>
-      </c>
-      <c r="C26" s="109"/>
-      <c r="D26" s="109"/>
-      <c r="E26" s="109"/>
-      <c r="F26" s="109"/>
-      <c r="G26" s="109"/>
-    </row>
-    <row r="27" spans="2:7" ht="3.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="28" spans="2:7" ht="19" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B28" s="108" t="s">
-        <v>294</v>
-      </c>
-      <c r="C28" s="108"/>
-      <c r="D28" s="108"/>
-      <c r="E28" s="108"/>
-      <c r="F28" s="108"/>
-      <c r="G28" s="108"/>
-    </row>
-    <row r="29" spans="2:7" ht="42.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="109" t="s">
-        <v>295</v>
-      </c>
-      <c r="C29" s="109"/>
-      <c r="D29" s="109"/>
-      <c r="E29" s="109"/>
-      <c r="F29" s="109"/>
-      <c r="G29" s="109"/>
-    </row>
-    <row r="30" spans="2:7" ht="5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="31" spans="2:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="110" t="s">
-        <v>296</v>
-      </c>
-      <c r="C31" s="110"/>
-      <c r="D31" s="110"/>
-      <c r="E31" s="110"/>
-      <c r="F31" s="110"/>
-      <c r="G31" s="110"/>
-    </row>
-    <row r="32" spans="2:7" ht="69" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="109" t="s">
-        <v>297</v>
-      </c>
-      <c r="C32" s="109"/>
-      <c r="D32" s="109"/>
-      <c r="E32" s="109"/>
-      <c r="F32" s="109"/>
-      <c r="G32" s="109"/>
-    </row>
-  </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B18:G18"/>
-    <mergeCell ref="B19:G19"/>
-    <mergeCell ref="B20:G20"/>
-    <mergeCell ref="B22:G22"/>
-    <mergeCell ref="B23:G23"/>
-    <mergeCell ref="B25:G25"/>
-    <mergeCell ref="B26:G26"/>
-    <mergeCell ref="B28:G28"/>
-    <mergeCell ref="B29:G29"/>
-    <mergeCell ref="B31:G31"/>
-    <mergeCell ref="B32:G32"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
 </file>
--- a/Loan_Portfolio_Dashboard.xlsx
+++ b/Loan_Portfolio_Dashboard.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data Science\Credit Analyst Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEBB37E1-8906-4AA4-9858-17330243DBB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74C21BE3-2BD4-493E-B731-6406907F352D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="745" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="745" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Business Problem" sheetId="1" r:id="rId1"/>
@@ -7888,8 +7888,8 @@
         <v>285</v>
       </c>
       <c r="C14" s="14">
-        <f>COUNTA('Officer Performance'!A4:A11)</f>
-        <v>0</v>
+        <f>COUNTA('Officer Performance'!C5:C12)</f>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -7897,8 +7897,8 @@
         <v>286</v>
       </c>
       <c r="C15" s="14">
-        <f>COUNTA('Portfolio Summary'!A22:A29)</f>
-        <v>0</v>
+        <f>COUNTA('Portfolio Summary'!C18:C21)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="17.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -7906,8 +7906,8 @@
         <v>287</v>
       </c>
       <c r="C16" s="14">
-        <f>COUNTA('Portfolio Summary'!A10:A17)</f>
-        <v>0</v>
+        <f>COUNTA('Portfolio Summary'!B6:B13)</f>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="2:7" ht="9" customHeight="1" x14ac:dyDescent="0.35"/>
